--- a/docs/Latency per message v2.0.0.xlsx
+++ b/docs/Latency per message v2.0.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\whghk\Desktop\Coding\Intellij\embellish_chat\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44527807-D53D-4F1F-B0D2-005BA4128E5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9563BAB-18E9-43F1-A5F6-2B7016B35C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{30AE5353-CC8E-4A31-864B-BE4B1A53EFC5}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t>v2.0.0/avg</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -61,15 +61,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>v2.1.0/min</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v2.1.0/avg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>v2.1.0/max</t>
+    <t>1GB RAM and 250 char</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -454,7 +446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B38E37E-D8A4-4D05-B5EE-C32E8023EE69}">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="2" width="19.796875" customWidth="1"/>
@@ -465,7 +457,7 @@
     <col min="7" max="7" width="16.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -478,17 +470,8 @@
       <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="E1" t="s">
-        <v>6</v>
-      </c>
-      <c r="F1" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -502,7 +485,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>10</v>
       </c>
@@ -516,7 +499,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>30</v>
       </c>
@@ -530,7 +513,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>50</v>
       </c>
@@ -544,7 +527,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>100</v>
       </c>
@@ -558,7 +541,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>150</v>
       </c>
@@ -572,7 +555,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>200</v>
       </c>
@@ -586,7 +569,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>300</v>
       </c>
@@ -600,7 +583,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>378</v>
       </c>
@@ -612,6 +595,11 @@
       </c>
       <c r="D10">
         <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+      <c r="A13" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
